--- a/06_方案乙_技术版/Demo/需知/tools/templates/需知_知识库_样本数据.xlsx
+++ b/06_方案乙_技术版/Demo/需知/tools/templates/需知_知识库_样本数据.xlsx
@@ -3772,7 +3772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3781,12 +3781,14 @@
     <col width="56" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>系统目录 · 样本数据（Demo 现用的虚构示例；黄色区域可直接改成公司真实数据，改完用 import_knowledge.py template 导入）</t>
+          <t>系统目录 · 样本数据（Demo 现用的虚构示例；黄色区域可直接改成公司真实数据，改完用 import_knowledge.py template 导入）　｜　G、H 两列可选：数据域与接口，填了就有「数据地图」</t>
         </is>
       </c>
     </row>
@@ -3821,6 +3823,16 @@
           <t>成熟度（成熟/试点/改动受控）</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>数据域（名称:关键词/关键词:时效；分号分隔）</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>接口（名称:类型:状态；分号分隔）</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3853,6 +3865,16 @@
           <t>成熟</t>
         </is>
       </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>报表数据集:报表/日报/周报/看板:日终</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>数据集配置 + 报表模板:配置:可用；订阅 / 定时分发任务:定时任务:可用</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3885,6 +3907,16 @@
           <t>成熟</t>
         </is>
       </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>行情日终:行情/结算价/收盘价/涨跌幅/涨跌停/主力合约/合约/K线/走势:T+1；持仓日终:持仓/持仓量/头寸/敞口/持仓盈亏:T+1；产品净值（同步自估值核算）:净值/单位净值/累计净值/份额:T+1；指数与比较基准:对标指数/指数/基准/超额收益/跟踪误差:T+1；历史数据:历史/回填/回测:T+1</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>SQL 视图 v_mkt_daily / v_pos_daily / v_nav_daily:SQL 视图:可用；数据集接口 /dwh/api/dataset:REST:可用</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3917,6 +3949,16 @@
           <t>成熟</t>
         </is>
       </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>实时行情:实时行情/行情/最新价/盘中/分钟线/K线/异动/涨跌幅:实时</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>行情推送 SDK:SDK:需申请订阅额度；REST 快照 /mkt/snapshot:REST:可用</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3949,235 +3991,376 @@
           <t>成熟·改动受控</t>
         </is>
       </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>实时持仓与资金:实时持仓/持仓/可用资金/保证金/保证金占用/风险度/资金/追保/资金缺口:实时；指令与成交:下单/报单/指令/成交/拒单/成交量:实时；限仓与风控参数:限仓/持仓限额/超限/事前风控/风控参数:实时</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>旁路查询接口 /trd/query（只读）:REST:可用；事前风控插件（改交易链路）:进程内插件:改动受控·需审批</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>RSK</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>风控系统</t>
+          <t>结算系统</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>风控部 + 技术部</t>
+          <t>技术部·交易组 + 结算部</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>风险指标、回撤、集中度、杠杆、预警、限额、风险度、日终指标</t>
+          <t>结算、结算单、结算价、手续费、盈亏、出入金、日终</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>日终指标表 + 预警规则配置</t>
+          <t>结算后生成日终文件与视图，供数据仓库同步</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>成熟</t>
+          <t>成熟·外购</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>结算数据:结算/结算单/结算价/手续费/盈亏/出入金/结算后:日终（结算后）</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>结算后日终文件:文件:可用；结算视图 v_settle_daily:SQL 视图:可用</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MSG</t>
+          <t>RSK</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>消息推送中心</t>
+          <t>风控系统</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>技术部·基础组</t>
+          <t>风控部 + 技术部</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>企业微信、邮件、短信、推送、提醒、通知、去重、模板消息</t>
+          <t>风险指标、回撤、集中度、杠杆、预警、限额、风险度、日终指标</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>统一推送 API，支持渠道与频控配置</t>
+          <t>日终指标表 + 预警规则配置</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
           <t>成熟</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>日终风险指标:风险指标/回撤/集中度/杠杆/VaR/风险度:T+1；预警规则与限额:预警/限额/阈值/超限:实时（规则）</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>日终指标表 t_risk_daily:SQL 表:可用；预警规则配置:配置:可用</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>OAM</t>
+          <t>MSG</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>OA 移动门户</t>
+          <t>消息推送中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>技术部·应用组</t>
+          <t>技术部·基础组</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>手机、移动、H5、单点登录、审批、待办</t>
+          <t>企业微信、邮件、短信、推送、提醒、通知、去重、模板消息</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>H5 嵌入 + SSO</t>
+          <t>统一推送 API，支持渠道与频控配置</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t>成熟</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>统一推送 API /msg/send:REST:可用；模板消息与频控配置:配置:可用</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>OAM</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>估值核算系统</t>
+          <t>OA 移动门户</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>资管运营 + 技术部</t>
+          <t>技术部·应用组</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>净值、估值、产品、份额、分红、T+1</t>
+          <t>手机、移动、H5、单点登录、审批、待办</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>日终净值文件 / 视图</t>
+          <t>H5 嵌入 + SSO</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>成熟·外购</t>
+          <t>成熟</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>H5 嵌入 + SSO:页面嵌入:可用；待办 / 审批流接口:REST:可用</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>IAM</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>权限中心</t>
+          <t>估值核算系统</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>技术部·基础组</t>
+          <t>资管运营 + 技术部</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>角色、数据权限、产品授权、部门、审计、留痕</t>
+          <t>净值、估值、产品、份额、分红、T+1</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>统一鉴权 SDK；数据权限按产品 / 部门维度</t>
+          <t>日终净值文件 / 视图</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>成熟</t>
+          <t>成熟·外购</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>产品估值:净值/单位净值/累计净值/估值/份额/分红/产品规模/估值核算:T+1</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>日终净值文件:文件:可用；估值视图 v_nav_daily（经数据仓库）:SQL 视图:可用</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>AIP</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>公司 AI 平台</t>
+          <t>客户管理系统</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>信息技术部</t>
+          <t>技术部·应用组 + 客户服务部</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>大模型、LLM、解析、摘要、文本、问答、生成</t>
+          <t>客户、资金账号、投资者、客户经理、适当性、联系方式</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>OpenAI 兼容 API，key 申请制</t>
+          <t>客户主数据接口（字段级权限，敏感字段脱敏输出）</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>试点</t>
+          <t>成熟</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>客户与账户主数据:客户/资金账号/投资者/账户/客户经理/适当性/客户管理:实时（主数据）</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>客户主数据接口 /crm/customer（脱敏输出）:REST:需申请字段权限</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>IAM</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>权限中心</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>技术部·基础组</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>角色、数据权限、产品授权、部门、审计、留痕</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>统一鉴权 SDK；数据权限按产品 / 部门维度</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>成熟</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>统一鉴权 SDK:SDK:可用；数据权限（产品 / 部门维度）配置:配置:可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>AIP</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>公司 AI 平台</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>信息技术部</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>大模型、LLM、解析、摘要、文本、问答、生成</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>OpenAI 兼容 API，key 申请制</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>试点</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>OpenAI 兼容 API:REST:需申请 key</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>ANN</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>公告采集服务</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>技术部·数据组</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>公告、交易所、抓取、保证金调整、手续费、涨跌停、解析</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>定时抓取五家交易所公告，提供原文与初步结构化字段</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>试点</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>说明：</t>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>交易所公告:公告/交易所公告/保证金调整/手续费调整/涨跌停调整/交易所通知/公告采集:事件（抓取后 10 分钟内）</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>公告原文 + 结构化字段 /ann/list:REST:试点·可用</t>
         </is>
       </c>
     </row>
